--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Этапы'!$A$1:$G$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Этапы'!$A$1:$G$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -74,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -85,6 +85,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -554,14 +557,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>27.09.2026</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(см. main)</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Ветка wip/v10-label-inside, осталось 5 пунктов доработки</t>
+          <t>Табличка переезжает внутрь и в старых проектах</t>
         </is>
       </c>
     </row>
@@ -728,46 +739,38 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>И2</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>2. Надёжность кода</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Правило: новый код интерфейса — в модуль своей подсистемы, в app.js только подключение</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>26.09.2026</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>46e94aa</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Действует с 26.09</t>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>В14</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>4. Мелочи интерфейса</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Табличка Г-коридора целиком внутри (сейчас в углу «Г» краем за стеной, центр внутри)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>не начато</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Найдено 27.09 при проверке В10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>З1</t>
+          <t>И2</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -777,22 +780,34 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Поиск краёв для автономера КП (А4) и счётчика элементов (Б1) — не запускался</t>
+          <t>Правило: новый код интерфейса — в модуль своей подсистемы, в app.js только подключение</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26.09.2026</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>46e94aa</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Действует с 26.09</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>З2</t>
+          <t>З1</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -802,7 +817,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Убрать мёртвый код одиночных элементов — вместе с решением, что делать с ними в старых проектах</t>
+          <t>Поиск краёв для автономера КП (А4) и счётчика элементов (Б1) — не запускался</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -817,17 +832,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Б3</t>
+          <t>З2</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>3. Функции по просьбе заказчика</t>
+          <t>2. Надёжность кода</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Поворот плана («повернуть нужно обязательно»)</t>
+          <t>Убрать мёртвый код одиночных элементов — вместе с решением, что делать с ними в старых проектах</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -842,7 +857,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Б4</t>
+          <t>Б3</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -852,7 +867,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Отмена и повтор действия (undo / redo)</t>
+          <t>Поворот плана («повернуть нужно обязательно»)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -867,7 +882,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Б5</t>
+          <t>Б4</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -877,7 +892,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Групповое выделение («обязательно для отелей»)</t>
+          <t>Отмена и повтор действия (undo / redo)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -892,7 +907,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>А5</t>
+          <t>Б5</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -902,7 +917,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Реквизиты с галочками: какие поля показывать в КП (свои и заказчика)</t>
+          <t>Групповое выделение («обязательно для отелей»)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -917,7 +932,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>А6</t>
+          <t>А5</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -927,7 +942,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Спецификация в Excel</t>
+          <t>Реквизиты с галочками: какие поля показывать в КП (свои и заказчика)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -942,7 +957,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Б6</t>
+          <t>А6</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -952,7 +967,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Этажи</t>
+          <t>Спецификация в Excel</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -967,7 +982,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Б7</t>
+          <t>Б6</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -977,7 +992,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Экспликация по комнатам</t>
+          <t>Этажи</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -992,7 +1007,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>А7</t>
+          <t>Б7</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1002,7 +1017,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Запоминать скидку и настройки по клиенту («у Иванова постоянно 10%»)</t>
+          <t>Экспликация по комнатам</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1017,17 +1032,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>В3</t>
+          <t>А7</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>4. Мелочи интерфейса</t>
+          <t>3. Функции по просьбе заказчика</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Вид «С картинками»: строка «Стандарт: не задан» / название стандарта над «Подобрать накладку»</t>
+          <t>Запоминать скидку и настройки по клиенту («у Иванова постоянно 10%»)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1037,16 +1052,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Фраза результата готова — ждёт вашего «да»</t>
-        </is>
-      </c>
+      <c r="G20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>В9</t>
+          <t>В3</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1056,7 +1067,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Панель «Стоимость»: процент скидки не противоречит сумме с личными скидками; поле не обрезает «%»</t>
+          <t>Вид «С картинками»: строка «Стандарт: не задан» / название стандарта над «Подобрать накладку»</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1066,12 +1077,16 @@
       </c>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Фраза результата готова — ждёт вашего «да»</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>В12</t>
+          <t>В9</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1081,7 +1096,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Окно поста без накладок: совет «измените отбор» один раз, нет ложного «выберите накладку» справа</t>
+          <t>Панель «Стоимость»: процент скидки не противоречит сумме с личными скидками; поле не обрезает «%»</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1096,7 +1111,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>В4</t>
+          <t>В12</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1106,7 +1121,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Подсказка «сузили: …» называет стандарт и при непустом отборе</t>
+          <t>Окно поста без накладок: совет «измените отбор» один раз, нет ложного «выберите накладку» справа</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1121,7 +1136,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>В6</t>
+          <t>В4</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1131,7 +1146,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Печать в КП — внахлёст на подпись, а не справа</t>
+          <t>Подсказка «сузили: …» называет стандарт и при непустом отборе</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1146,7 +1161,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>З4</t>
+          <t>В6</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1156,7 +1171,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Фокус Tab не уезжает на соседнюю строку при слиянии строк скидки</t>
+          <t>Печать в КП — внахлёст на подпись, а не справа</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1171,22 +1186,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>З3</t>
+          <t>З4</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>5. Ваше решение</t>
+          <t>4. Мелочи интерфейса</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Пост со своей скидкой, равной общей (10 и 10) — сливать ли со строкой без своей скидки</t>
+          <t>Фокус Tab не уезжает на соседнюю строку при слиянии строк скидки</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>ждёт вашего решения</t>
+          <t>не начато</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1196,7 +1211,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>З5</t>
+          <t>З3</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1206,7 +1221,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>НДС нового проекта по умолчанию «Начислить сверху» — оставить или сменить</t>
+          <t>Пост со своей скидкой, равной общей (10 и 10) — сливать ли со строкой без своей скидки</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1221,36 +1236,32 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>А1</t>
+          <t>З5</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>6. Ждёт ответа заказчика</t>
+          <t>5. Ваше решение</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Наценка в КП — видна клиенту строкой или сразу в цене</t>
+          <t>НДС нового проекта по умолчанию «Начислить сверху» — оставить или сменить</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>ждёт заказчика</t>
+          <t>ждёт вашего решения</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Вы отложили 24.09</t>
-        </is>
-      </c>
+      <c r="G28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>А8</t>
+          <t>А1</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1260,7 +1271,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Два документа «Расчёт» и «КП» — чем «Расчёт» отличается</t>
+          <t>Наценка в КП — видна клиенту строкой или сразу в цене</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1270,12 +1281,16 @@
       </c>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Вы отложили 24.09</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Б8</t>
+          <t>А8</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1285,7 +1300,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Вертикальные / горизонтальные рамки (разные артикулы)</t>
+          <t>Два документа «Расчёт» и «КП» — чем «Расчёт» отличается</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1300,7 +1315,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Г1</t>
+          <t>Б8</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1310,7 +1325,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Подсветка клавиш, часть B (NEVE, Eikon Flat — 9,60 € за светодиод)</t>
+          <t>Вертикальные / горизонтальные рамки (разные артикулы)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1325,7 +1340,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Е1</t>
+          <t>Г1</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1335,7 +1350,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Код функции изделия — замена клавиш при смене серии; опечатка 19105.B</t>
+          <t>Подсветка клавиш, часть B (NEVE, Eikon Flat — 9,60 € за светодиод)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1350,7 +1365,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Е2</t>
+          <t>Е1</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1360,7 +1375,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Фото 698 артикулов</t>
+          <t>Код функции изделия — замена клавиш при смене серии; опечатка 19105.B</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1375,7 +1390,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Е3</t>
+          <t>Е2</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1385,7 +1400,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Подсветка NEVE / Eikon Flat; звонковые кнопки 220 В или 00935</t>
+          <t>Фото 698 артикулов</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1400,7 +1415,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Е4</t>
+          <t>Е3</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1410,7 +1425,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Аксессуары 02973, 02974, 02965.1 и таблица «механизм → аксессуар»</t>
+          <t>Подсветка NEVE / Eikon Flat; звонковые кнопки 220 В или 00935</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1425,7 +1440,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Е5</t>
+          <t>Е4</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1435,7 +1450,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Логотип EPG в векторе, «Соглашения сторон», формат номера КП</t>
+          <t>Аксессуары 02973, 02974, 02965.1 и таблица «механизм → аксессуар»</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1450,7 +1465,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Е6</t>
+          <t>Е5</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1460,7 +1475,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Типы пользователей; коды 2 и 4 в «Группе доступа»</t>
+          <t>Логотип EPG в векторе, «Соглашения сторон», формат номера КП</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1475,7 +1490,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Е7</t>
+          <t>Е6</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1485,7 +1500,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Прайс со статусами (в наличии / под заказ / снят, замены), номенклатура LINEA</t>
+          <t>Типы пользователей; коды 2 и 4 в «Группе доступа»</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1500,7 +1515,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Е8</t>
+          <t>Е7</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1510,7 +1525,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Немецкий стандарт без накладки на 3 модуля — по умолчанию 2 или 4 (сейчас 2)</t>
+          <t>Прайс со статусами (в наличии / под заказ / снят, замены), номенклатура LINEA</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1520,45 +1535,41 @@
       </c>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Связано с З6</t>
-        </is>
-      </c>
+      <c r="G39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Д1</t>
+          <t>Е8</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>7. Сервис на продажу</t>
+          <t>6. Ждёт ответа заказчика</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Личные кабинеты, многопользовательский режим</t>
+          <t>Немецкий стандарт без накладки на 3 модуля — по умолчанию 2 или 4 (сейчас 2)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
+          <t>ждёт заказчика</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Обсудить приоритеты с заказчиком</t>
+          <t>Связано с З6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Д2</t>
+          <t>Д1</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1568,7 +1579,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Уровни доступа демо / менеджер / профи, покупка брендов, логотип и подпись по тарифу</t>
+          <t>Личные кабинеты, многопользовательский режим</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1578,12 +1589,16 @@
       </c>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Обсудить приоритеты с заказчиком</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Д3</t>
+          <t>Д2</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1593,7 +1608,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Версии проекта и история КП; курс евро версионировать вместе с проектом</t>
+          <t>Уровни доступа демо / менеджер / профи, покупка брендов, логотип и подпись по тарифу</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1608,7 +1623,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Д4</t>
+          <t>Д3</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1618,7 +1633,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Обязательные поля проекта, проверка уникальности КП</t>
+          <t>Версии проекта и история КП; курс евро версионировать вместе с проектом</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -1633,7 +1648,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Д5</t>
+          <t>Д4</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1643,7 +1658,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Сравнение спецификаций разных компаний по одному объекту</t>
+          <t>Обязательные поля проекта, проверка уникальности КП</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -1658,7 +1673,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Д6</t>
+          <t>Д5</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1668,7 +1683,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Прайсы в других валютах и с другой наценкой под новые бренды</t>
+          <t>Сравнение спецификаций разных компаний по одному объекту</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -1683,22 +1698,22 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Ж1</t>
+          <t>Д6</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>8. Отложено заказчиком</t>
+          <t>7. Сервис на продажу</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Распознавание плана чертежа (кнопки скрыты с 21.09)</t>
+          <t>Прайсы в других валютах и с другой наценкой под новые бренды</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>отложено заказчиком</t>
+          <t>не начато</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -1708,7 +1723,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Ж2</t>
+          <t>Ж1</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1718,7 +1733,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Межсерийные адаптеры 09623, 16723</t>
+          <t>Распознавание плана чертежа (кнопки скрыты с 21.09)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -1733,7 +1748,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Ж3</t>
+          <t>Ж2</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1743,7 +1758,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Расценки работ по операциям</t>
+          <t>Межсерийные адаптеры 09623, 16723</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -1758,7 +1773,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Ж4</t>
+          <t>Ж3</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -1768,7 +1783,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Битрикс</t>
+          <t>Расценки работ по операциям</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -1778,49 +1793,41 @@
       </c>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Не обязателен</t>
-        </is>
-      </c>
+      <c r="G49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>В2</t>
+          <t>Ж4</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>4. Мелочи интерфейса</t>
+          <t>8. Отложено заказчиком</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Плашка «Под эту комнату накладок нет» — совет один раз</t>
+          <t>Битрикс</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>26.09.2026</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>d7204e3</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
+          <t>отложено заказчиком</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Не обязателен</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>В1</t>
+          <t>В2</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -1830,7 +1837,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Клик по табличке комнаты при «Разместить» ставит пост</t>
+          <t>Плашка «Под эту комнату накладок нет» — совет один раз</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -1845,7 +1852,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>56d4916</t>
+          <t>d7204e3</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
@@ -1853,17 +1860,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Б1</t>
+          <t>В1</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>3. Функции по просьбе заказчика</t>
+          <t>4. Мелочи интерфейса</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Убрать одиночные элементы с плана (счётчик «Элементов»)</t>
+          <t>Клик по табличке комнаты при «Разместить» ставит пост</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -1878,7 +1885,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>69762c3</t>
+          <t>56d4916</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
@@ -1886,7 +1893,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>А2</t>
+          <t>Б1</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -1896,7 +1903,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Скидка на отдельные позиции</t>
+          <t>Убрать одиночные элементы с плана (счётчик «Элементов»)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -1911,7 +1918,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>f9c3143</t>
+          <t>69762c3</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
@@ -1919,7 +1926,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Б2</t>
+          <t>А2</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -1929,7 +1936,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Лист монтажника: «общая сборка» / «взрыв-схема»</t>
+          <t>Скидка на отдельные позиции</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -1944,7 +1951,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>8511c47</t>
+          <t>f9c3143</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -1952,7 +1959,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>А4</t>
+          <t>Б2</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -1962,7 +1969,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Автонумерация КП EPG-2026-0001</t>
+          <t>Лист монтажника: «общая сборка» / «взрыв-схема»</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -1972,16 +1979,20 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr"/>
+          <t>26.09.2026</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>8511c47</t>
+        </is>
+      </c>
       <c r="G55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>А3</t>
+          <t>А4</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -1991,7 +2002,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>НДС — три режима</t>
+          <t>Автонумерация КП EPG-2026-0001</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2007,8 +2018,37 @@
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>А3</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>3. Функции по просьбе заказчика</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>НДС — три режима</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G56"/>
+  <autoFilter ref="A1:G57"/>
   <conditionalFormatting sqref="A2:G256">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$D2="сделано"</formula>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>(см. main)</t>
+          <t>b2b1544</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -727,14 +727,14 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
+          <t>в работе</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Сразу после В10 (ваше решение 26.09). На экране ничего не меняется</t>
+          <t>27.09: шаги 1–2 из 3 окна поста готовы; точка отката — метка do-razdeleniya-app-js</t>
         </is>
       </c>
     </row>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -734,7 +734,7 @@
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>27.09: шаги 1–2 из 3 окна поста готовы; точка отката — метка do-razdeleniya-app-js</t>
+          <t>27.09: окно поста вынесено (js/postBuilder.js), app.js 6093→4682 строк; дальше — комнаты, КП, клики холста. Точка отката — метка do-razdeleniya-app-js</t>
         </is>
       </c>
     </row>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -734,7 +734,7 @@
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>27.09: окно поста вынесено (js/postBuilder.js), app.js 6093→4682 строк; дальше — комнаты, КП, клики холста. Точка отката — метка do-razdeleniya-app-js</t>
+          <t>27.09: вынесены окно поста (js/postBuilder.js) и комнаты (js/rooms.js); app.js 6093→4559 строк; дальше — КП и лист монтажника, клики холста. Точка отката — метка do-razdeleniya-app-js</t>
         </is>
       </c>
     </row>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -734,7 +734,7 @@
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>27.09: вынесены окно поста (js/postBuilder.js) и комнаты (js/rooms.js); app.js 6093→4559 строк; дальше — КП и лист монтажника, клики холста. Точка отката — метка do-razdeleniya-app-js</t>
+          <t>27.09: вынесены окно поста (js/postBuilder.js), комнаты (js/rooms.js), КП и лист монтажника (js/docs.js); app.js 6093→4004 строк; дальше — клики холста, распознавание помещений. Точка отката — метка do-razdeleniya-app-js</t>
         </is>
       </c>
     </row>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -734,7 +734,7 @@
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>27.09: вынесены окно поста (js/postBuilder.js), комнаты (js/rooms.js), КП и лист монтажника (js/docs.js); app.js 6093→4004 строк; дальше — клики холста, распознавание помещений. Точка отката — метка do-razdeleniya-app-js</t>
+          <t>27.09: вынесены окно поста, комнаты, КП и лист монтажника, ввод на холсте (js/postBuilder|rooms|docs|canvasInput.js); app.js 6093→3804 строк; остался кусок «распознавание и разметка помещений». Точка отката — метка do-razdeleniya-app-js</t>
         </is>
       </c>
     </row>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -727,14 +727,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>047787c</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>27.09: вынесены окно поста, комнаты, КП и лист монтажника, ввод на холсте (js/postBuilder|rooms|docs|canvasInput.js); app.js 6093→3804 строк; остался кусок «распознавание и разметка помещений». Точка отката — метка do-razdeleniya-app-js</t>
+          <t>app.js 6093→3501 строк; модули postBuilder, rooms, docs, canvasInput, roomDetect, wallScope; на экране ничего не изменилось. Точка отката — метка do-razdeleniya-app-js</t>
         </is>
       </c>
     </row>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Этапы'!$A$1:$G$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Этапы'!$A$1:$G$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -863,134 +863,158 @@
       <c r="G12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Б3</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>3. Функции по просьбе заказчика</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Поворот плана («повернуть нужно обязательно»)</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>З9</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>2. Надёжность кода</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Тесты ловят поломку цены и личной скидки в КП, имён комнат в документе, групп света в листе монтажника</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Найдено при разбиении app.js (дыра была и раньше)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Б4</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>3. Функции по просьбе заказчика</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Отмена и повтор действия (undo / redo)</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>З10</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>2. Надёжность кода</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Тесты ловят поломку перетаскивания: порог клик/перенос, отмена Esc, сохранение позиции, блокировка пробелом</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Найдено при разбиении app.js</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Б5</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>3. Функции по просьбе заказчика</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Групповое выделение («обязательно для отелей»)</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>З8</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>2. Надёжность кода</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Тесты ловят поломку правки вершин контура комнаты</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>не начато</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Найдено при разбиении app.js</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>А5</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>3. Функции по просьбе заказчика</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Реквизиты с галочками: какие поля показывать в КП (свои и заказчика)</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>З11</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>2. Надёжность кода</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Тесты ловят поломку инструмента «Разметка»: очистка, притяжение к точке, пересборка при удалении линии</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>не начато</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Найдено при разбиении app.js</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>А6</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>3. Функции по просьбе заказчика</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Спецификация в Excel</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>З12</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>2. Надёжность кода</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Инструмент тестов правильно вырезает последнюю функцию модуля</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>не начато</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Найдено при разбиении app.js</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Б6</t>
+          <t>Б3</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1000,7 +1024,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Этажи</t>
+          <t>Поворот плана («повернуть нужно обязательно»)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1015,7 +1039,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Б7</t>
+          <t>Б4</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1025,7 +1049,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Экспликация по комнатам</t>
+          <t>Отмена и повтор действия (undo / redo)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1040,7 +1064,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>А7</t>
+          <t>Б5</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1050,7 +1074,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Запоминать скидку и настройки по клиенту («у Иванова постоянно 10%»)</t>
+          <t>Групповое выделение («обязательно для отелей»)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1065,17 +1089,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>В3</t>
+          <t>А5</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>4. Мелочи интерфейса</t>
+          <t>3. Функции по просьбе заказчика</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Вид «С картинками»: строка «Стандарт: не задан» / название стандарта над «Подобрать накладку»</t>
+          <t>Реквизиты с галочками: какие поля показывать в КП (свои и заказчика)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1085,26 +1109,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Фраза результата готова — ждёт вашего «да»</t>
-        </is>
-      </c>
+      <c r="G21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>В9</t>
+          <t>А6</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>4. Мелочи интерфейса</t>
+          <t>3. Функции по просьбе заказчика</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Панель «Стоимость»: процент скидки не противоречит сумме с личными скидками; поле не обрезает «%»</t>
+          <t>Спецификация в Excel</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1119,17 +1139,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>В12</t>
+          <t>Б6</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>4. Мелочи интерфейса</t>
+          <t>3. Функции по просьбе заказчика</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Окно поста без накладок: совет «измените отбор» один раз, нет ложного «выберите накладку» справа</t>
+          <t>Этажи</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1144,17 +1164,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>В4</t>
+          <t>Б7</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>4. Мелочи интерфейса</t>
+          <t>3. Функции по просьбе заказчика</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Подсказка «сузили: …» называет стандарт и при непустом отборе</t>
+          <t>Экспликация по комнатам</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1169,17 +1189,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>В6</t>
+          <t>А7</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>4. Мелочи интерфейса</t>
+          <t>3. Функции по просьбе заказчика</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Печать в КП — внахлёст на подпись, а не справа</t>
+          <t>Запоминать скидку и настройки по клиенту («у Иванова постоянно 10%»)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1194,7 +1214,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>З4</t>
+          <t>В3</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1204,7 +1224,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Фокус Tab не уезжает на соседнюю строку при слиянии строк скидки</t>
+          <t>Вид «С картинками»: строка «Стандарт: не задан» / название стандарта над «Подобрать накладку»</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1214,27 +1234,31 @@
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Фраза результата готова — ждёт вашего «да»</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>З3</t>
+          <t>В9</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>5. Ваше решение</t>
+          <t>4. Мелочи интерфейса</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Пост со своей скидкой, равной общей (10 и 10) — сливать ли со строкой без своей скидки</t>
+          <t>Панель «Стоимость»: процент скидки не противоречит сумме с личными скидками; поле не обрезает «%»</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>ждёт вашего решения</t>
+          <t>не начато</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1244,22 +1268,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>З5</t>
+          <t>В12</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>5. Ваше решение</t>
+          <t>4. Мелочи интерфейса</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>НДС нового проекта по умолчанию «Начислить сверху» — оставить или сменить</t>
+          <t>Окно поста без накладок: совет «измените отбор» один раз, нет ложного «выберите накладку» справа</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>ждёт вашего решения</t>
+          <t>не начато</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -1269,51 +1293,47 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>А1</t>
+          <t>В4</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>6. Ждёт ответа заказчика</t>
+          <t>4. Мелочи интерфейса</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Наценка в КП — видна клиенту строкой или сразу в цене</t>
+          <t>Подсказка «сузили: …» называет стандарт и при непустом отборе</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>ждёт заказчика</t>
+          <t>не начато</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Вы отложили 24.09</t>
-        </is>
-      </c>
+      <c r="G29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>А8</t>
+          <t>В6</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>6. Ждёт ответа заказчика</t>
+          <t>4. Мелочи интерфейса</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Два документа «Расчёт» и «КП» — чем «Расчёт» отличается</t>
+          <t>Печать в КП — внахлёст на подпись, а не справа</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>ждёт заказчика</t>
+          <t>не начато</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -1323,22 +1343,22 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Б8</t>
+          <t>З4</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>6. Ждёт ответа заказчика</t>
+          <t>4. Мелочи интерфейса</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Вертикальные / горизонтальные рамки (разные артикулы)</t>
+          <t>Фокус Tab не уезжает на соседнюю строку при слиянии строк скидки</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>ждёт заказчика</t>
+          <t>не начато</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -1348,22 +1368,22 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Г1</t>
+          <t>З3</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>6. Ждёт ответа заказчика</t>
+          <t>5. Ваше решение</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Подсветка клавиш, часть B (NEVE, Eikon Flat — 9,60 € за светодиод)</t>
+          <t>Пост со своей скидкой, равной общей (10 и 10) — сливать ли со строкой без своей скидки</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>ждёт заказчика</t>
+          <t>ждёт вашего решения</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -1373,22 +1393,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Е1</t>
+          <t>З5</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>6. Ждёт ответа заказчика</t>
+          <t>5. Ваше решение</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Код функции изделия — замена клавиш при смене серии; опечатка 19105.B</t>
+          <t>НДС нового проекта по умолчанию «Начислить сверху» — оставить или сменить</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>ждёт заказчика</t>
+          <t>ждёт вашего решения</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -1398,7 +1418,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Е2</t>
+          <t>А1</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1408,7 +1428,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Фото 698 артикулов</t>
+          <t>Наценка в КП — видна клиенту строкой или сразу в цене</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1418,12 +1438,16 @@
       </c>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Вы отложили 24.09</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Е3</t>
+          <t>А8</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1433,7 +1457,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Подсветка NEVE / Eikon Flat; звонковые кнопки 220 В или 00935</t>
+          <t>Два документа «Расчёт» и «КП» — чем «Расчёт» отличается</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1448,7 +1472,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Е4</t>
+          <t>Б8</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1458,7 +1482,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Аксессуары 02973, 02974, 02965.1 и таблица «механизм → аксессуар»</t>
+          <t>Вертикальные / горизонтальные рамки (разные артикулы)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1473,7 +1497,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Е5</t>
+          <t>Г1</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1483,7 +1507,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Логотип EPG в векторе, «Соглашения сторон», формат номера КП</t>
+          <t>Подсветка клавиш, часть B (NEVE, Eikon Flat — 9,60 € за светодиод)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1498,7 +1522,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Е6</t>
+          <t>Е1</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1508,7 +1532,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Типы пользователей; коды 2 и 4 в «Группе доступа»</t>
+          <t>Код функции изделия — замена клавиш при смене серии; опечатка 19105.B</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1523,7 +1547,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Е7</t>
+          <t>Е2</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1533,7 +1557,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Прайс со статусами (в наличии / под заказ / снят, замены), номенклатура LINEA</t>
+          <t>Фото 698 артикулов</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1548,7 +1572,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Е8</t>
+          <t>Е3</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1558,7 +1582,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Немецкий стандарт без накладки на 3 модуля — по умолчанию 2 или 4 (сейчас 2)</t>
+          <t>Подсветка NEVE / Eikon Flat; звонковые кнопки 220 В или 00935</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1568,60 +1592,52 @@
       </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Связано с З6</t>
-        </is>
-      </c>
+      <c r="G40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Д1</t>
+          <t>Е4</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>7. Сервис на продажу</t>
+          <t>6. Ждёт ответа заказчика</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Личные кабинеты, многопользовательский режим</t>
+          <t>Аксессуары 02973, 02974, 02965.1 и таблица «механизм → аксессуар»</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
+          <t>ждёт заказчика</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Обсудить приоритеты с заказчиком</t>
-        </is>
-      </c>
+      <c r="G41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Д2</t>
+          <t>Е5</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>7. Сервис на продажу</t>
+          <t>6. Ждёт ответа заказчика</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Уровни доступа демо / менеджер / профи, покупка брендов, логотип и подпись по тарифу</t>
+          <t>Логотип EPG в векторе, «Соглашения сторон», формат номера КП</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
+          <t>ждёт заказчика</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -1631,22 +1647,22 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Д3</t>
+          <t>Е6</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>7. Сервис на продажу</t>
+          <t>6. Ждёт ответа заказчика</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Версии проекта и история КП; курс евро версионировать вместе с проектом</t>
+          <t>Типы пользователей; коды 2 и 4 в «Группе доступа»</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
+          <t>ждёт заказчика</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -1656,22 +1672,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Д4</t>
+          <t>Е7</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>7. Сервис на продажу</t>
+          <t>6. Ждёт ответа заказчика</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Обязательные поля проекта, проверка уникальности КП</t>
+          <t>Прайс со статусами (в наличии / под заказ / снят, замены), номенклатура LINEA</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
+          <t>ждёт заказчика</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -1681,32 +1697,36 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Д5</t>
+          <t>Е8</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>7. Сервис на продажу</t>
+          <t>6. Ждёт ответа заказчика</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Сравнение спецификаций разных компаний по одному объекту</t>
+          <t>Немецкий стандарт без накладки на 3 модуля — по умолчанию 2 или 4 (сейчас 2)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
+          <t>ждёт заказчика</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Связано с З6</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Д6</t>
+          <t>Д1</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1716,7 +1736,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Прайсы в других валютах и с другой наценкой под новые бренды</t>
+          <t>Личные кабинеты, многопользовательский режим</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -1726,27 +1746,31 @@
       </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Обсудить приоритеты с заказчиком</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Ж1</t>
+          <t>Д2</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>8. Отложено заказчиком</t>
+          <t>7. Сервис на продажу</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Распознавание плана чертежа (кнопки скрыты с 21.09)</t>
+          <t>Уровни доступа демо / менеджер / профи, покупка брендов, логотип и подпись по тарифу</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>отложено заказчиком</t>
+          <t>не начато</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -1756,22 +1780,22 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Ж2</t>
+          <t>Д3</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>8. Отложено заказчиком</t>
+          <t>7. Сервис на продажу</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Межсерийные адаптеры 09623, 16723</t>
+          <t>Версии проекта и история КП; курс евро версионировать вместе с проектом</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>отложено заказчиком</t>
+          <t>не начато</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -1781,22 +1805,22 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Ж3</t>
+          <t>Д4</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>8. Отложено заказчиком</t>
+          <t>7. Сервис на продажу</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Расценки работ по операциям</t>
+          <t>Обязательные поля проекта, проверка уникальности КП</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>отложено заказчиком</t>
+          <t>не начато</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -1806,211 +1830,171 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Ж4</t>
+          <t>Д5</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>8. Отложено заказчиком</t>
+          <t>7. Сервис на продажу</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Битрикс</t>
+          <t>Сравнение спецификаций разных компаний по одному объекту</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>отложено заказчиком</t>
+          <t>не начато</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>Не обязателен</t>
-        </is>
-      </c>
+      <c r="G50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>В2</t>
+          <t>Д6</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>4. Мелочи интерфейса</t>
+          <t>7. Сервис на продажу</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Плашка «Под эту комнату накладок нет» — совет один раз</t>
+          <t>Прайсы в других валютах и с другой наценкой под новые бренды</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>26.09.2026</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>d7204e3</t>
-        </is>
-      </c>
+          <t>не начато</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>В1</t>
+          <t>Ж1</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>4. Мелочи интерфейса</t>
+          <t>8. Отложено заказчиком</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Клик по табличке комнаты при «Разместить» ставит пост</t>
+          <t>Распознавание плана чертежа (кнопки скрыты с 21.09)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>26.09.2026</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>56d4916</t>
-        </is>
-      </c>
+          <t>отложено заказчиком</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Б1</t>
+          <t>Ж2</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>3. Функции по просьбе заказчика</t>
+          <t>8. Отложено заказчиком</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Убрать одиночные элементы с плана (счётчик «Элементов»)</t>
+          <t>Межсерийные адаптеры 09623, 16723</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>26.09.2026</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>69762c3</t>
-        </is>
-      </c>
+          <t>отложено заказчиком</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>А2</t>
+          <t>Ж3</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>3. Функции по просьбе заказчика</t>
+          <t>8. Отложено заказчиком</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Скидка на отдельные позиции</t>
+          <t>Расценки работ по операциям</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>26.09.2026</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>f9c3143</t>
-        </is>
-      </c>
+          <t>отложено заказчиком</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Б2</t>
+          <t>Ж4</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>3. Функции по просьбе заказчика</t>
+          <t>8. Отложено заказчиком</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Лист монтажника: «общая сборка» / «взрыв-схема»</t>
+          <t>Битрикс</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>26.09.2026</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>8511c47</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr"/>
+          <t>отложено заказчиком</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Не обязателен</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>А4</t>
+          <t>В2</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>3. Функции по просьбе заказчика</t>
+          <t>4. Мелочи интерфейса</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Автонумерация КП EPG-2026-0001</t>
+          <t>Плашка «Под эту комнату накладок нет» — совет один раз</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2020,43 +2004,208 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr"/>
+          <t>26.09.2026</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>d7204e3</t>
+        </is>
+      </c>
       <c r="G56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>В1</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>4. Мелочи интерфейса</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Клик по табличке комнаты при «Разместить» ставит пост</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>26.09.2026</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>56d4916</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Б1</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>3. Функции по просьбе заказчика</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Убрать одиночные элементы с плана (счётчик «Элементов»)</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>26.09.2026</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>69762c3</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>А2</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>3. Функции по просьбе заказчика</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Скидка на отдельные позиции</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>26.09.2026</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>f9c3143</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Б2</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>3. Функции по просьбе заказчика</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Лист монтажника: «общая сборка» / «взрыв-схема»</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>26.09.2026</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>8511c47</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>А4</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>3. Функции по просьбе заказчика</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Автонумерация КП EPG-2026-0001</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
           <t>А3</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>3. Функции по просьбе заказчика</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>НДС — три режима</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>сделано</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>24.09.2026</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G57"/>
+  <autoFilter ref="A1:G62"/>
   <conditionalFormatting sqref="A2:G256">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$D2="сделано"</formula>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -888,7 +888,11 @@
           <t>28.09.2026</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>88e41ec</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Найдено при разбиении app.js (дыра была и раньше)</t>
@@ -913,10 +917,14 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
       <c r="F14" s="6" t="inlineStr"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
@@ -942,7 +950,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>не начато</t>
+          <t>в работе</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr"/>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -925,7 +925,11 @@
           <t>28.09.2026</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>3bfba3e</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Найдено при разбиении app.js</t>
@@ -950,10 +954,14 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
       <c r="F15" s="6" t="inlineStr"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
@@ -979,7 +987,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>не начато</t>
+          <t>в работе</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr"/>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -962,7 +962,11 @@
           <t>28.09.2026</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>7cdbbf8</t>
+        </is>
+      </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Найдено при разбиении app.js</t>
@@ -987,10 +991,14 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
       <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="6" t="inlineStr">
         <is>
@@ -1016,7 +1024,7 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>не начато</t>
+          <t>в работе</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr"/>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -999,7 +999,11 @@
           <t>28.09.2026</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>08bcd70</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Найдено при разбиении app.js</t>
@@ -1024,14 +1028,18 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
       <c r="F17" s="6" t="inlineStr"/>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Найдено при разбиении app.js</t>
+          <t>Правка была в 1e647e9; тесты закрепляют её на всех модулях</t>
         </is>
       </c>
     </row>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -594,14 +594,22 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>3792773</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Тот же корень, что В10</t>
+          <t>Г/П-комнаты сохраняют поля при пересборке; стандарт переносится у всех комнат</t>
         </is>
       </c>
     </row>
@@ -2235,6 +2243,64 @@
       </c>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>В15</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>1. Деньги и потеря данных</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Удалил стену и нарисовал заново — комната среди других исчезает вместе с полями (у любой формы)</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>не начато</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n"/>
+      <c r="F63" s="2" t="n"/>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Найдено 29.09 при В13; владелец: «согласен» — отдельный пункт</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>З13</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>2. Надёжность кода</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Тесты: перенос полей не должен брать точку таблички или сырой полюс (мутации MX1/MX2 не пойманы)</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>не начато</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n"/>
+      <c r="F64" s="2" t="n"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Хвост проверки В13, 29.09</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G62"/>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2262,14 +2262,22 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="n"/>
-      <c r="F63" s="2" t="n"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>154a9fa</t>
+        </is>
+      </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Найдено 29.09 при В13; владелец: «согласен» — отдельный пункт</t>
+          <t>Комната возвращается со своими полями и ценой; память в проекте</t>
         </is>
       </c>
     </row>
@@ -2291,14 +2299,51 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="n"/>
-      <c r="F64" s="2" t="n"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>154a9fa</t>
+        </is>
+      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Хвост проверки В13, 29.09</t>
+          <t>Тесты с жёстким ожиданием; MX1/MX2 красят</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>З14</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>2. Надёжность кода</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Тесты: память исчезнувших комнат не должна попадать на постороннюю комнату (мутации MY1/MY2/MY8 не пойманы)</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>не начато</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n"/>
+      <c r="F65" s="2" t="n"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Хвост проверки В15, 29.09</t>
         </is>
       </c>
     </row>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -2336,14 +2336,22 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="n"/>
-      <c r="F65" s="2" t="n"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>01acd84</t>
+        </is>
+      </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Хвост проверки В15, 29.09</t>
+          <t>Тесты Ж7–Ж9; все 8 мутаций памяти красят</t>
         </is>
       </c>
     </row>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -1269,14 +1269,22 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>660f88b</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Фраза результата готова — ждёт вашего «да»</t>
+          <t>Строка «Стандарт: …» в виде «С картинками»</t>
         </is>
       </c>
     </row>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -1069,12 +1069,24 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>05.10.2026</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7add36a</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Оба варианта (только чертёж / весь план) и оба угла (90° / любой); весь план — на холсте, в КП и листе монтажника; подписи прямые, цена не меняется</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -1106,12 +1106,24 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>07.10.2026</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>b09dc37</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Кнопки «Отменить/Вернуть», Ctrl+Z/Y, 50 шагов: посты, стены, разметка, комнаты, окно поста, поворот, очистка, «Убрать план», чертёж; смета возвращается; настройки и вид не откатываются</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -1143,12 +1143,24 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>10.10.2026</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>69a896b</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Рамка мышью и Ctrl+клик, «Выделено: N», карточка группы с суммой; группу можно перетащить, сдвинуть стрелками, удалить; каждый пост в своей комнате; отмена одним шагом. Только посты</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Этапы'!$A$1:$G$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Этапы'!$A$1:$G$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1165,7 +1165,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>А5</t>
+          <t>Б9</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1175,22 +1175,34 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Реквизиты с галочками: какие поля показывать в КП (свои и заказчика)</t>
+          <t>Копирование постов («да, с избранным на N комбинаций»)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>11.10.2026</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>aabbb78</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Ctrl+C / Ctrl+V: копии встают под мышью в том же расположении, считаются по своей комнате, отмена одним шагом; свои номера проходных; накладка, уже подходящая комнате, не меняется (и при «Разместить»); два сообщения с крестиком. Не сделано: «избранное на N комбинаций» — вопрос заказчику. В бэклоге: В22 (автосдвиг выносит пост за стену), В23 (снятая с производства накладка).</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>А6</t>
+          <t>А5</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1200,7 +1212,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Спецификация в Excel</t>
+          <t>Реквизиты с галочками: какие поля показывать в КП (свои и заказчика)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1215,7 +1227,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Б6</t>
+          <t>А6</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1225,7 +1237,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Этажи</t>
+          <t>Спецификация в Excel</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Б7</t>
+          <t>Б6</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1250,7 +1262,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Экспликация по комнатам</t>
+          <t>Этажи</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1265,7 +1277,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>А7</t>
+          <t>Б7</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1275,7 +1287,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Запоминать скидку и настройки по клиенту («у Иванова постоянно 10%»)</t>
+          <t>Экспликация по комнатам</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1290,44 +1302,32 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>В3</t>
+          <t>А7</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>4. Мелочи интерфейса</t>
+          <t>3. Функции по просьбе заказчика</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Вид «С картинками»: строка «Стандарт: не задан» / название стандарта над «Подобрать накладку»</t>
+          <t>Запоминать скидку и настройки по клиенту («у Иванова постоянно 10%»)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>660f88b</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Строка «Стандарт: …» в виде «С картинками»</t>
-        </is>
-      </c>
+          <t>не начато</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>В9</t>
+          <t>В3</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1337,22 +1337,34 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Панель «Стоимость»: процент скидки не противоречит сумме с личными скидками; поле не обрезает «%»</t>
+          <t>Вид «С картинками»: строка «Стандарт: не задан» / название стандарта над «Подобрать накладку»</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>660f88b</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Строка «Стандарт: …» в виде «С картинками»</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>В12</t>
+          <t>В9</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1362,7 +1374,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Окно поста без накладок: совет «измените отбор» один раз, нет ложного «выберите накладку» справа</t>
+          <t>Панель «Стоимость»: процент скидки не противоречит сумме с личными скидками; поле не обрезает «%»</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1377,7 +1389,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>В4</t>
+          <t>В12</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1387,7 +1399,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Подсказка «сузили: …» называет стандарт и при непустом отборе</t>
+          <t>Окно поста без накладок: совет «измените отбор» один раз, нет ложного «выберите накладку» справа</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1402,7 +1414,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>В6</t>
+          <t>В4</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1412,7 +1424,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Печать в КП — внахлёст на подпись, а не справа</t>
+          <t>Подсказка «сузили: …» называет стандарт и при непустом отборе</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1427,7 +1439,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>З4</t>
+          <t>В6</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1437,7 +1449,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Фокус Tab не уезжает на соседнюю строку при слиянии строк скидки</t>
+          <t>Печать в КП — внахлёст на подпись, а не справа</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1452,22 +1464,22 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>З3</t>
+          <t>З4</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>5. Ваше решение</t>
+          <t>4. Мелочи интерфейса</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Пост со своей скидкой, равной общей (10 и 10) — сливать ли со строкой без своей скидки</t>
+          <t>Фокус Tab не уезжает на соседнюю строку при слиянии строк скидки</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>ждёт вашего решения</t>
+          <t>не начато</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -1477,7 +1489,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>З5</t>
+          <t>З3</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1487,7 +1499,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>НДС нового проекта по умолчанию «Начислить сверху» — оставить или сменить</t>
+          <t>Пост со своей скидкой, равной общей (10 и 10) — сливать ли со строкой без своей скидки</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1502,36 +1514,32 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>А1</t>
+          <t>З5</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>6. Ждёт ответа заказчика</t>
+          <t>5. Ваше решение</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Наценка в КП — видна клиенту строкой или сразу в цене</t>
+          <t>НДС нового проекта по умолчанию «Начислить сверху» — оставить или сменить</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>ждёт заказчика</t>
+          <t>ждёт вашего решения</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Вы отложили 24.09</t>
-        </is>
-      </c>
+      <c r="G34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>А8</t>
+          <t>А1</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1541,7 +1549,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Два документа «Расчёт» и «КП» — чем «Расчёт» отличается</t>
+          <t>Наценка в КП — видна клиенту строкой или сразу в цене</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1551,12 +1559,16 @@
       </c>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Вы отложили 24.09</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Б8</t>
+          <t>А8</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1566,7 +1578,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Вертикальные / горизонтальные рамки (разные артикулы)</t>
+          <t>Два документа «Расчёт» и «КП» — чем «Расчёт» отличается</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1581,7 +1593,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Г1</t>
+          <t>Б8</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1591,7 +1603,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Подсветка клавиш, часть B (NEVE, Eikon Flat — 9,60 € за светодиод)</t>
+          <t>Вертикальные / горизонтальные рамки (разные артикулы)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1606,7 +1618,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Е1</t>
+          <t>Г1</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1616,7 +1628,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Код функции изделия — замена клавиш при смене серии; опечатка 19105.B</t>
+          <t>Подсветка клавиш, часть B (NEVE, Eikon Flat — 9,60 € за светодиод)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1631,7 +1643,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Е2</t>
+          <t>Е1</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1641,7 +1653,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Фото 698 артикулов</t>
+          <t>Код функции изделия — замена клавиш при смене серии; опечатка 19105.B</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1656,7 +1668,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Е3</t>
+          <t>Е2</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1666,7 +1678,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Подсветка NEVE / Eikon Flat; звонковые кнопки 220 В или 00935</t>
+          <t>Фото 698 артикулов</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1681,7 +1693,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Е4</t>
+          <t>Е3</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1691,7 +1703,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Аксессуары 02973, 02974, 02965.1 и таблица «механизм → аксессуар»</t>
+          <t>Подсветка NEVE / Eikon Flat; звонковые кнопки 220 В или 00935</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1706,7 +1718,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Е5</t>
+          <t>Е4</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1716,7 +1728,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Логотип EPG в векторе, «Соглашения сторон», формат номера КП</t>
+          <t>Аксессуары 02973, 02974, 02965.1 и таблица «механизм → аксессуар»</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1731,7 +1743,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Е6</t>
+          <t>Е5</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1741,7 +1753,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Типы пользователей; коды 2 и 4 в «Группе доступа»</t>
+          <t>Логотип EPG в векторе, «Соглашения сторон», формат номера КП</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -1756,7 +1768,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Е7</t>
+          <t>Е6</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1766,7 +1778,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Прайс со статусами (в наличии / под заказ / снят, замены), номенклатура LINEA</t>
+          <t>Типы пользователей; коды 2 и 4 в «Группе доступа»</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -1781,7 +1793,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Е8</t>
+          <t>Е7</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1791,7 +1803,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Немецкий стандарт без накладки на 3 модуля — по умолчанию 2 или 4 (сейчас 2)</t>
+          <t>Прайс со статусами (в наличии / под заказ / снят, замены), номенклатура LINEA</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -1801,45 +1813,41 @@
       </c>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Связано с З6</t>
-        </is>
-      </c>
+      <c r="G45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Д1</t>
+          <t>Е8</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>7. Сервис на продажу</t>
+          <t>6. Ждёт ответа заказчика</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Личные кабинеты, многопользовательский режим</t>
+          <t>Немецкий стандарт без накладки на 3 модуля — по умолчанию 2 или 4 (сейчас 2)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
+          <t>ждёт заказчика</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Обсудить приоритеты с заказчиком</t>
+          <t>Связано с З6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Д2</t>
+          <t>Д1</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1849,7 +1857,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Уровни доступа демо / менеджер / профи, покупка брендов, логотип и подпись по тарифу</t>
+          <t>Личные кабинеты, многопользовательский режим</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -1859,12 +1867,16 @@
       </c>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Обсудить приоритеты с заказчиком</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Д3</t>
+          <t>Д2</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1874,7 +1886,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Версии проекта и история КП; курс евро версионировать вместе с проектом</t>
+          <t>Уровни доступа демо / менеджер / профи, покупка брендов, логотип и подпись по тарифу</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -1889,7 +1901,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Д4</t>
+          <t>Д3</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -1899,7 +1911,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Обязательные поля проекта, проверка уникальности КП</t>
+          <t>Версии проекта и история КП; курс евро версионировать вместе с проектом</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -1914,7 +1926,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Д5</t>
+          <t>Д4</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1924,7 +1936,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Сравнение спецификаций разных компаний по одному объекту</t>
+          <t>Обязательные поля проекта, проверка уникальности КП</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -1939,7 +1951,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Д6</t>
+          <t>Д5</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -1949,7 +1961,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Прайсы в других валютах и с другой наценкой под новые бренды</t>
+          <t>Сравнение спецификаций разных компаний по одному объекту</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -1964,22 +1976,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Ж1</t>
+          <t>Д6</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>8. Отложено заказчиком</t>
+          <t>7. Сервис на продажу</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Распознавание плана чертежа (кнопки скрыты с 21.09)</t>
+          <t>Прайсы в других валютах и с другой наценкой под новые бренды</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>отложено заказчиком</t>
+          <t>не начато</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -1989,7 +2001,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Ж2</t>
+          <t>Ж1</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -1999,7 +2011,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Межсерийные адаптеры 09623, 16723</t>
+          <t>Распознавание плана чертежа (кнопки скрыты с 21.09)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2014,7 +2026,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Ж3</t>
+          <t>Ж2</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2024,7 +2036,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Расценки работ по операциям</t>
+          <t>Межсерийные адаптеры 09623, 16723</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2039,7 +2051,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Ж4</t>
+          <t>Ж3</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2049,7 +2061,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Битрикс</t>
+          <t>Расценки работ по операциям</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2059,49 +2071,41 @@
       </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Не обязателен</t>
-        </is>
-      </c>
+      <c r="G55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>В2</t>
+          <t>Ж4</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>4. Мелочи интерфейса</t>
+          <t>8. Отложено заказчиком</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Плашка «Под эту комнату накладок нет» — совет один раз</t>
+          <t>Битрикс</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>26.09.2026</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>d7204e3</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr"/>
+          <t>отложено заказчиком</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Не обязателен</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>В1</t>
+          <t>В2</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -2111,7 +2115,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Клик по табличке комнаты при «Разместить» ставит пост</t>
+          <t>Плашка «Под эту комнату накладок нет» — совет один раз</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2126,7 +2130,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>56d4916</t>
+          <t>d7204e3</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
@@ -2134,17 +2138,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Б1</t>
+          <t>В1</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>3. Функции по просьбе заказчика</t>
+          <t>4. Мелочи интерфейса</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Убрать одиночные элементы с плана (счётчик «Элементов»)</t>
+          <t>Клик по табличке комнаты при «Разместить» ставит пост</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2159,7 +2163,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>69762c3</t>
+          <t>56d4916</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -2167,7 +2171,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>А2</t>
+          <t>Б1</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -2177,7 +2181,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Скидка на отдельные позиции</t>
+          <t>Убрать одиночные элементы с плана (счётчик «Элементов»)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2192,7 +2196,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>f9c3143</t>
+          <t>69762c3</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -2200,7 +2204,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Б2</t>
+          <t>А2</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2210,7 +2214,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Лист монтажника: «общая сборка» / «взрыв-схема»</t>
+          <t>Скидка на отдельные позиции</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2225,7 +2229,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>8511c47</t>
+          <t>f9c3143</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -2233,7 +2237,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>А4</t>
+          <t>Б2</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -2243,7 +2247,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Автонумерация КП EPG-2026-0001</t>
+          <t>Лист монтажника: «общая сборка» / «взрыв-схема»</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2253,16 +2257,20 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr"/>
+          <t>26.09.2026</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>8511c47</t>
+        </is>
+      </c>
       <c r="G61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>А3</t>
+          <t>А4</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2272,7 +2280,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>НДС — три режима</t>
+          <t>Автонумерация КП EPG-2026-0001</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2291,17 +2299,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>В15</t>
+          <t>А3</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>1. Деньги и потеря данных</t>
+          <t>3. Функции по просьбе заказчика</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Удалил стену и нарисовал заново — комната среди других исчезает вместе с полями (у любой формы)</t>
+          <t>НДС — три режима</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2311,34 +2319,26 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>154a9fa</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>Комната возвращается со своими полями и ценой; память в проекте</t>
-        </is>
-      </c>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>З13</t>
+          <t>В15</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>2. Надёжность кода</t>
+          <t>1. Деньги и потеря данных</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Тесты: перенос полей не должен брать точку таблички или сырой полюс (мутации MX1/MX2 не пойманы)</t>
+          <t>Удалил стену и нарисовал заново — комната среди других исчезает вместе с полями (у любой формы)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -2358,49 +2358,86 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Тесты с жёстким ожиданием; MX1/MX2 красят</t>
+          <t>Комната возвращается со своими полями и ценой; память в проекте</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>З13</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>2. Надёжность кода</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Тесты: перенос полей не должен брать точку таблички или сырой полюс (мутации MX1/MX2 не пойманы)</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>154a9fa</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Тесты с жёстким ожиданием; MX1/MX2 красят</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
           <t>З14</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>2. Надёжность кода</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Тесты: память исчезнувших комнат не должна попадать на постороннюю комнату (мутации MY1/MY2/MY8 не пойманы)</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>сделано</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>01acd84</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>Тесты Ж7–Ж9; все 8 мутаций памяти красят</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G62"/>
+  <autoFilter ref="A1:G66"/>
   <conditionalFormatting sqref="A2:G256">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$D2="сделано"</formula>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -1217,12 +1217,24 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>03.10.2026</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>8e7129e</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>«Мои реквизиты» (общие для всех проектов) и «Реквизиты заказчика» (свои у проекта): ФИО, телефон и e-mail печатаются всегда, остальное — по галочке «показывать в КП»; «Разработчик» под своей галочкой. Перепроверено в браузере 11.10: снятые поля в шапке КП не печатаются, после перезагрузки всё на месте.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1242,12 +1254,24 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>03.10.2026</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>4ace33c</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Кнопка «Спецификация Excel» рядом с КП: файл .xlsx с листами «Спецификация» (как в КП) и «По артикулам» (поставщику); числа — числами, итог — формулой. Перепроверено 11.10: итоги файла равны КП до копейки. Состязательной проверки не было.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -685,12 +685,24 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>359fad6</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Строки итогов сходятся до копейки в панели, КП и Excel; одно школьное округление на всю программу, как в Excel. В бэклоге В26: копейка на ручном курсе от 15 штук одного товара.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -710,12 +722,24 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>359fad6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Пустой проект КП не открывает (сообщение), номер не занимает; ручной номер счётчик года не двигает.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1478,12 +1502,24 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>359fad6</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Печать поверх подписи, подпись видна сквозь неё, имя под подписью не перекрыто.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -744,110 +744,110 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>В26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1. Деньги и потеря данных</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Строка спецификации считается как в обычном счёте: количество × цена = сумма, суммы строк = «Оборудование»</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>a6c342e</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Счёт по изделиям; скидка, материалы и работы — от напечатанного «Оборудования»; одна цена поста в окне поста, подсказке, свойствах, раскладке КП; оба листа Excel. Проверено настоящим Excel. Уже выставленные КП при открытии сдвигаются на копейки–рубли.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>И1</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>2. Надёжность кода</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Разбиение app.js на модули по одному куску: окно поста → комнаты → КП и лист монтажника → клики по холсту</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>28.09.2026</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>047787c</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>app.js 6093→3501 строк; модули postBuilder, rooms, docs, canvasInput, roomDetect, wallScope; на экране ничего не изменилось. Точка отката — метка do-razdeleniya-app-js</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>В14</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>4. Мелочи интерфейса</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Табличка Г-коридора целиком внутри (сейчас в углу «Г» краем за стеной, центр внутри)</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>не начато</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>Найдено 27.09 при проверке В10</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>И2</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>2. Надёжность кода</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Правило: новый код интерфейса — в модуль своей подсистемы, в app.js только подключение</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>26.09.2026</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>46e94aa</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Действует с 26.09</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>З1</t>
+          <t>И2</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -857,22 +857,34 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Поиск краёв для автономера КП (А4) и счётчика элементов (Б1) — не запускался</t>
+          <t>Правило: новый код интерфейса — в модуль своей подсистемы, в app.js только подключение</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26.09.2026</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>46e94aa</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Действует с 26.09</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>З2</t>
+          <t>З1</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -882,7 +894,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Убрать мёртвый код одиночных элементов — вместе с решением, что делать с ними в старых проектах</t>
+          <t>Поиск краёв для автономера КП (А4) и счётчика элементов (Б1) — не запускался</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -895,46 +907,34 @@
       <c r="G12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>З9</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>З2</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>2. Надёжность кода</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Тесты ловят поломку цены и личной скидки в КП, имён комнат в документе, групп света в листе монтажника</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>88e41ec</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Найдено при разбиении app.js (дыра была и раньше)</t>
-        </is>
-      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Убрать мёртвый код одиночных элементов — вместе с решением, что делать с ними в старых проектах</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>не начато</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>З10</t>
+          <t>З9</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Тесты ловят поломку перетаскивания: порог клик/перенос, отмена Esc, сохранение позиции, блокировка пробелом</t>
+          <t>Тесты ловят поломку цены и личной скидки в КП, имён комнат в документе, групп света в листе монтажника</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -959,19 +959,19 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>3bfba3e</t>
+          <t>88e41ec</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Найдено при разбиении app.js</t>
+          <t>Найдено при разбиении app.js (дыра была и раньше)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>З8</t>
+          <t>З10</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Тесты ловят поломку правки вершин контура комнаты</t>
+          <t>Тесты ловят поломку перетаскивания: порог клик/перенос, отмена Esc, сохранение позиции, блокировка пробелом</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>7cdbbf8</t>
+          <t>3bfba3e</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -1008,7 +1008,7 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>З11</t>
+          <t>З8</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Тесты ловят поломку инструмента «Разметка»: очистка, притяжение к точке, пересборка при удалении линии</t>
+          <t>Тесты ловят поломку правки вершин контура комнаты</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>08bcd70</t>
+          <t>7cdbbf8</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -1045,77 +1045,77 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
+          <t>З11</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>2. Надёжность кода</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Тесты ловят поломку инструмента «Разметка»: очистка, притяжение к точке, пересборка при удалении линии</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>08bcd70</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Найдено при разбиении app.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
           <t>З12</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>2. Надёжность кода</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Инструмент тестов правильно вырезает последнюю функцию модуля</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>28.09.2026</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr"/>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>Правка была в 1e647e9; тесты закрепляют её на всех модулях</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Б3</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>3. Функции по просьбе заказчика</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Поворот плана («повернуть нужно обязательно»)</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>05.10.2026</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>7add36a</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Оба варианта (только чертёж / весь план) и оба угла (90° / любой); весь план — на холсте, в КП и листе монтажника; подписи прямые, цена не меняется</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Б4</t>
+          <t>Б3</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Отмена и повтор действия (undo / redo)</t>
+          <t>Поворот плана («повернуть нужно обязательно»)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>07.10.2026</t>
+          <t>05.10.2026</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>b09dc37</t>
+          <t>7add36a</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Кнопки «Отменить/Вернуть», Ctrl+Z/Y, 50 шагов: посты, стены, разметка, комнаты, окно поста, поворот, очистка, «Убрать план», чертёж; смета возвращается; настройки и вид не откатываются</t>
+          <t>Оба варианта (только чертёж / весь план) и оба угла (90° / любой); весь план — на холсте, в КП и листе монтажника; подписи прямые, цена не меняется</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Б5</t>
+          <t>Б4</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Групповое выделение («обязательно для отелей»)</t>
+          <t>Отмена и повтор действия (undo / redo)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1172,24 +1172,24 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10.10.2026</t>
+          <t>07.10.2026</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>69a896b</t>
+          <t>b09dc37</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Рамка мышью и Ctrl+клик, «Выделено: N», карточка группы с суммой; группу можно перетащить, сдвинуть стрелками, удалить; каждый пост в своей комнате; отмена одним шагом. Только посты</t>
+          <t>Кнопки «Отменить/Вернуть», Ctrl+Z/Y, 50 шагов: посты, стены, разметка, комнаты, окно поста, поворот, очистка, «Убрать план», чертёж; смета возвращается; настройки и вид не откатываются</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Б9</t>
+          <t>Б5</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Копирование постов («да, с избранным на N комбинаций»)</t>
+          <t>Групповое выделение («обязательно для отелей»)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1209,24 +1209,24 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11.10.2026</t>
+          <t>10.10.2026</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>aabbb78</t>
+          <t>69a896b</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Ctrl+C / Ctrl+V: копии встают под мышью в том же расположении, считаются по своей комнате, отмена одним шагом; свои номера проходных; накладка, уже подходящая комнате, не меняется (и при «Разместить»); два сообщения с крестиком. Не сделано: «избранное на N комбинаций» — вопрос заказчику. В бэклоге: В22 (автосдвиг выносит пост за стену), В23 (снятая с производства накладка).</t>
+          <t>Рамка мышью и Ctrl+клик, «Выделено: N», карточка группы с суммой; группу можно перетащить, сдвинуть стрелками, удалить; каждый пост в своей комнате; отмена одним шагом. Только посты</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>А5</t>
+          <t>Б9</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Реквизиты с галочками: какие поля показывать в КП (свои и заказчика)</t>
+          <t>Копирование постов («да, с избранным на N комбинаций»)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1246,24 +1246,24 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>03.10.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8e7129e</t>
+          <t>aabbb78</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>«Мои реквизиты» (общие для всех проектов) и «Реквизиты заказчика» (свои у проекта): ФИО, телефон и e-mail печатаются всегда, остальное — по галочке «показывать в КП»; «Разработчик» под своей галочкой. Перепроверено в браузере 11.10: снятые поля в шапке КП не печатаются, после перезагрузки всё на месте.</t>
+          <t>Ctrl+C / Ctrl+V: копии встают под мышью в том же расположении, считаются по своей комнате, отмена одним шагом; свои номера проходных; накладка, уже подходящая комнате, не меняется (и при «Разместить»); два сообщения с крестиком. Не сделано: «избранное на N комбинаций» — вопрос заказчику. В бэклоге: В22 (автосдвиг выносит пост за стену), В23 (снятая с производства накладка).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>А6</t>
+          <t>А5</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Спецификация в Excel</t>
+          <t>Реквизиты с галочками: какие поля показывать в КП (свои и заказчика)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1288,19 +1288,19 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4ace33c</t>
+          <t>8e7129e</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Кнопка «Спецификация Excel» рядом с КП: файл .xlsx с листами «Спецификация» (как в КП) и «По артикулам» (поставщику); числа — числами, итог — формулой. Перепроверено 11.10: итоги файла равны КП до копейки. Состязательной проверки не было.</t>
+          <t>«Мои реквизиты» (общие для всех проектов) и «Реквизиты заказчика» (свои у проекта): ФИО, телефон и e-mail печатаются всегда, остальное — по галочке «показывать в КП»; «Разработчик» под своей галочкой. Перепроверено в браузере 11.10: снятые поля в шапке КП не печатаются, после перезагрузки всё на месте.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Б6</t>
+          <t>А6</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1310,22 +1310,34 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Этажи</t>
+          <t>Спецификация в Excel</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>03.10.2026</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>4ace33c</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Кнопка «Спецификация Excel» рядом с КП: файл .xlsx с листами «Спецификация» (как в КП) и «По артикулам» (поставщику); числа — числами, итог — формулой. Перепроверено 11.10: итоги файла равны КП до копейки. Состязательной проверки не было.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Б7</t>
+          <t>Б6</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1335,7 +1347,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Экспликация по комнатам</t>
+          <t>Этажи</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1350,7 +1362,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>А7</t>
+          <t>Б7</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1360,7 +1372,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Запоминать скидку и настройки по клиенту («у Иванова постоянно 10%»)</t>
+          <t>Экспликация по комнатам</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1375,44 +1387,32 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>В3</t>
+          <t>А7</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>4. Мелочи интерфейса</t>
+          <t>3. Функции по просьбе заказчика</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Вид «С картинками»: строка «Стандарт: не задан» / название стандарта над «Подобрать накладку»</t>
+          <t>Запоминать скидку и настройки по клиенту («у Иванова постоянно 10%»)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>660f88b</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Строка «Стандарт: …» в виде «С картинками»</t>
-        </is>
-      </c>
+          <t>не начато</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>В9</t>
+          <t>В3</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1422,22 +1422,34 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Панель «Стоимость»: процент скидки не противоречит сумме с личными скидками; поле не обрезает «%»</t>
+          <t>Вид «С картинками»: строка «Стандарт: не задан» / название стандарта над «Подобрать накладку»</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>660f88b</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Строка «Стандарт: …» в виде «С картинками»</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>В12</t>
+          <t>В9</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1447,7 +1459,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Окно поста без накладок: совет «измените отбор» один раз, нет ложного «выберите накладку» справа</t>
+          <t>Панель «Стоимость»: процент скидки не противоречит сумме с личными скидками; поле не обрезает «%»</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1462,7 +1474,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>В4</t>
+          <t>В12</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1472,7 +1484,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Подсказка «сузили: …» называет стандарт и при непустом отборе</t>
+          <t>Окно поста без накладок: совет «измените отбор» один раз, нет ложного «выберите накладку» справа</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1487,7 +1499,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>В6</t>
+          <t>В4</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1497,34 +1509,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Печать в КП — внахлёст на подпись, а не справа</t>
+          <t>Подсказка «сузили: …» называет стандарт и при непустом отборе</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>13.10.2026</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>359fad6</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Печать поверх подписи, подпись видна сквозь неё, имя под подписью не перекрыто.</t>
-        </is>
-      </c>
+          <t>не начато</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>З4</t>
+          <t>В6</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1534,37 +1534,49 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Фокус Tab не уезжает на соседнюю строку при слиянии строк скидки</t>
+          <t>Печать в КП — внахлёст на подпись, а не справа</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>359fad6</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Печать поверх подписи, подпись видна сквозь неё, имя под подписью не перекрыто.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>З3</t>
+          <t>З4</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>5. Ваше решение</t>
+          <t>4. Мелочи интерфейса</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Пост со своей скидкой, равной общей (10 и 10) — сливать ли со строкой без своей скидки</t>
+          <t>Фокус Tab не уезжает на соседнюю строку при слиянии строк скидки</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>ждёт вашего решения</t>
+          <t>не начато</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -1574,7 +1586,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>З5</t>
+          <t>З3</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1584,7 +1596,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>НДС нового проекта по умолчанию «Начислить сверху» — оставить или сменить</t>
+          <t>Пост со своей скидкой, равной общей (10 и 10) — сливать ли со строкой без своей скидки</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1599,36 +1611,32 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>А1</t>
+          <t>З5</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>6. Ждёт ответа заказчика</t>
+          <t>5. Ваше решение</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Наценка в КП — видна клиенту строкой или сразу в цене</t>
+          <t>НДС нового проекта по умолчанию «Начислить сверху» — оставить или сменить</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>ждёт заказчика</t>
+          <t>ждёт вашего решения</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Вы отложили 24.09</t>
-        </is>
-      </c>
+      <c r="G35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>А8</t>
+          <t>А1</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1638,7 +1646,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Два документа «Расчёт» и «КП» — чем «Расчёт» отличается</t>
+          <t>Наценка в КП — видна клиенту строкой или сразу в цене</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1648,12 +1656,16 @@
       </c>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Вы отложили 24.09</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Б8</t>
+          <t>А8</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1663,7 +1675,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Вертикальные / горизонтальные рамки (разные артикулы)</t>
+          <t>Два документа «Расчёт» и «КП» — чем «Расчёт» отличается</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1678,7 +1690,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Г1</t>
+          <t>Б8</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1688,7 +1700,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Подсветка клавиш, часть B (NEVE, Eikon Flat — 9,60 € за светодиод)</t>
+          <t>Вертикальные / горизонтальные рамки (разные артикулы)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1703,7 +1715,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Е1</t>
+          <t>Г1</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1713,7 +1725,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Код функции изделия — замена клавиш при смене серии; опечатка 19105.B</t>
+          <t>Подсветка клавиш, часть B (NEVE, Eikon Flat — 9,60 € за светодиод)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1728,7 +1740,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Е2</t>
+          <t>Е1</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1738,7 +1750,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Фото 698 артикулов</t>
+          <t>Код функции изделия — замена клавиш при смене серии; опечатка 19105.B</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1753,7 +1765,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Е3</t>
+          <t>Е2</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1763,7 +1775,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Подсветка NEVE / Eikon Flat; звонковые кнопки 220 В или 00935</t>
+          <t>Фото 698 артикулов</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1778,7 +1790,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Е4</t>
+          <t>Е3</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1788,7 +1800,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Аксессуары 02973, 02974, 02965.1 и таблица «механизм → аксессуар»</t>
+          <t>Подсветка NEVE / Eikon Flat; звонковые кнопки 220 В или 00935</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1803,7 +1815,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Е5</t>
+          <t>Е4</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1813,7 +1825,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Логотип EPG в векторе, «Соглашения сторон», формат номера КП</t>
+          <t>Аксессуары 02973, 02974, 02965.1 и таблица «механизм → аксессуар»</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -1828,7 +1840,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Е6</t>
+          <t>Е5</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1838,7 +1850,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Типы пользователей; коды 2 и 4 в «Группе доступа»</t>
+          <t>Логотип EPG в векторе, «Соглашения сторон», формат номера КП</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -1853,7 +1865,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Е7</t>
+          <t>Е6</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1863,7 +1875,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Прайс со статусами (в наличии / под заказ / снят, замены), номенклатура LINEA</t>
+          <t>Типы пользователей; коды 2 и 4 в «Группе доступа»</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -1878,7 +1890,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Е8</t>
+          <t>Е7</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1888,7 +1900,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Немецкий стандарт без накладки на 3 модуля — по умолчанию 2 или 4 (сейчас 2)</t>
+          <t>Прайс со статусами (в наличии / под заказ / снят, замены), номенклатура LINEA</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -1898,45 +1910,41 @@
       </c>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Связано с З6</t>
-        </is>
-      </c>
+      <c r="G46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Д1</t>
+          <t>Е8</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>7. Сервис на продажу</t>
+          <t>6. Ждёт ответа заказчика</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Личные кабинеты, многопользовательский режим</t>
+          <t>Немецкий стандарт без накладки на 3 модуля — по умолчанию 2 или 4 (сейчас 2)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
+          <t>ждёт заказчика</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Обсудить приоритеты с заказчиком</t>
+          <t>Связано с З6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Д2</t>
+          <t>Д1</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1946,7 +1954,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Уровни доступа демо / менеджер / профи, покупка брендов, логотип и подпись по тарифу</t>
+          <t>Личные кабинеты, многопользовательский режим</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -1956,12 +1964,16 @@
       </c>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Обсудить приоритеты с заказчиком</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Д3</t>
+          <t>Д2</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -1971,7 +1983,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Версии проекта и история КП; курс евро версионировать вместе с проектом</t>
+          <t>Уровни доступа демо / менеджер / профи, покупка брендов, логотип и подпись по тарифу</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -1986,7 +1998,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Д4</t>
+          <t>Д3</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1996,7 +2008,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Обязательные поля проекта, проверка уникальности КП</t>
+          <t>Версии проекта и история КП; курс евро версионировать вместе с проектом</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2011,7 +2023,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Д5</t>
+          <t>Д4</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2021,7 +2033,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Сравнение спецификаций разных компаний по одному объекту</t>
+          <t>Обязательные поля проекта, проверка уникальности КП</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2036,7 +2048,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Д6</t>
+          <t>Д5</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2046,7 +2058,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Прайсы в других валютах и с другой наценкой под новые бренды</t>
+          <t>Сравнение спецификаций разных компаний по одному объекту</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2061,22 +2073,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Ж1</t>
+          <t>Д6</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>8. Отложено заказчиком</t>
+          <t>7. Сервис на продажу</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Распознавание плана чертежа (кнопки скрыты с 21.09)</t>
+          <t>Прайсы в других валютах и с другой наценкой под новые бренды</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>отложено заказчиком</t>
+          <t>не начато</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -2086,7 +2098,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Ж2</t>
+          <t>Ж1</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2096,7 +2108,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Межсерийные адаптеры 09623, 16723</t>
+          <t>Распознавание плана чертежа (кнопки скрыты с 21.09)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2111,7 +2123,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Ж3</t>
+          <t>Ж2</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2121,7 +2133,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Расценки работ по операциям</t>
+          <t>Межсерийные адаптеры 09623, 16723</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2136,7 +2148,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Ж4</t>
+          <t>Ж3</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2146,7 +2158,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Битрикс</t>
+          <t>Расценки работ по операциям</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2156,49 +2168,41 @@
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Не обязателен</t>
-        </is>
-      </c>
+      <c r="G56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>В2</t>
+          <t>Ж4</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>4. Мелочи интерфейса</t>
+          <t>8. Отложено заказчиком</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Плашка «Под эту комнату накладок нет» — совет один раз</t>
+          <t>Битрикс</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>26.09.2026</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>d7204e3</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr"/>
+          <t>отложено заказчиком</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Не обязателен</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>В1</t>
+          <t>В2</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2208,7 +2212,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Клик по табличке комнаты при «Разместить» ставит пост</t>
+          <t>Плашка «Под эту комнату накладок нет» — совет один раз</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2223,7 +2227,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>56d4916</t>
+          <t>d7204e3</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -2231,17 +2235,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Б1</t>
+          <t>В1</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>3. Функции по просьбе заказчика</t>
+          <t>4. Мелочи интерфейса</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Убрать одиночные элементы с плана (счётчик «Элементов»)</t>
+          <t>Клик по табличке комнаты при «Разместить» ставит пост</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2256,7 +2260,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>69762c3</t>
+          <t>56d4916</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -2264,7 +2268,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>А2</t>
+          <t>Б1</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2274,7 +2278,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Скидка на отдельные позиции</t>
+          <t>Убрать одиночные элементы с плана (счётчик «Элементов»)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2289,7 +2293,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>f9c3143</t>
+          <t>69762c3</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -2297,7 +2301,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Б2</t>
+          <t>А2</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -2307,7 +2311,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Лист монтажника: «общая сборка» / «взрыв-схема»</t>
+          <t>Скидка на отдельные позиции</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2322,7 +2326,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>8511c47</t>
+          <t>f9c3143</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
@@ -2330,7 +2334,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>А4</t>
+          <t>Б2</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2340,7 +2344,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Автонумерация КП EPG-2026-0001</t>
+          <t>Лист монтажника: «общая сборка» / «взрыв-схема»</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2350,16 +2354,20 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr"/>
+          <t>26.09.2026</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>8511c47</t>
+        </is>
+      </c>
       <c r="G62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>А3</t>
+          <t>А4</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -2369,7 +2377,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>НДС — три режима</t>
+          <t>Автонумерация КП EPG-2026-0001</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2388,17 +2396,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>В15</t>
+          <t>А3</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>1. Деньги и потеря данных</t>
+          <t>3. Функции по просьбе заказчика</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Удалил стену и нарисовал заново — комната среди других исчезает вместе с полями (у любой формы)</t>
+          <t>НДС — три режима</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -2408,34 +2416,26 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>154a9fa</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Комната возвращается со своими полями и ценой; память в проекте</t>
-        </is>
-      </c>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>З13</t>
+          <t>В15</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>2. Надёжность кода</t>
+          <t>1. Деньги и потеря данных</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Тесты: перенос полей не должен брать точку таблички или сырой полюс (мутации MX1/MX2 не пойманы)</t>
+          <t>Удалил стену и нарисовал заново — комната среди других исчезает вместе с полями (у любой формы)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -2455,42 +2455,79 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Тесты с жёстким ожиданием; MX1/MX2 красят</t>
+          <t>Комната возвращается со своими полями и ценой; память в проекте</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>З13</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>2. Надёжность кода</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Тесты: перенос полей не должен брать точку таблички или сырой полюс (мутации MX1/MX2 не пойманы)</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>154a9fa</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Тесты с жёстким ожиданием; MX1/MX2 красят</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
           <t>З14</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>2. Надёжность кода</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Тесты: память исчезнувших комнат не должна попадать на постороннюю комнату (мутации MY1/MY2/MY8 не пойманы)</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>01acd84</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>Тесты Ж7–Ж9; все 8 мутаций памяти красят</t>
         </is>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -781,110 +781,110 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>В23</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>1. Деньги и потеря данных</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Снятая с производства накладка остаётся в посте при копировании и «Разместить», если подходит комнате</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>15.10.2026</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>ee488a2</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Подходящая снятая накладка не подменяется (пост 82,18 €, а не 66,22 €); неподходящая меняется, как обычная; новым постам не предлагается. В бэклоге: В27 (цвет комнаты), В29 (пометка в окне поста).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>И1</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>2. Надёжность кода</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Разбиение app.js на модули по одному куску: окно поста → комнаты → КП и лист монтажника → клики по холсту</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>28.09.2026</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>047787c</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>app.js 6093→3501 строк; модули postBuilder, rooms, docs, canvasInput, roomDetect, wallScope; на экране ничего не изменилось. Точка отката — метка do-razdeleniya-app-js</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>В14</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>4. Мелочи интерфейса</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Табличка Г-коридора целиком внутри (сейчас в углу «Г» краем за стеной, центр внутри)</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>не начато</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr"/>
-      <c r="F10" s="6" t="inlineStr"/>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Найдено 27.09 при проверке В10</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>И2</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2. Надёжность кода</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Правило: новый код интерфейса — в модуль своей подсистемы, в app.js только подключение</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>26.09.2026</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>46e94aa</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Действует с 26.09</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>З1</t>
+          <t>И2</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -894,22 +894,34 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Поиск краёв для автономера КП (А4) и счётчика элементов (Б1) — не запускался</t>
+          <t>Правило: новый код интерфейса — в модуль своей подсистемы, в app.js только подключение</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>26.09.2026</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>46e94aa</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Действует с 26.09</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>З2</t>
+          <t>З1</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -919,7 +931,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Убрать мёртвый код одиночных элементов — вместе с решением, что делать с ними в старых проектах</t>
+          <t>Поиск краёв для автономера КП (А4) и счётчика элементов (Б1) — не запускался</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -932,46 +944,34 @@
       <c r="G13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>З9</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>З2</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>2. Надёжность кода</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Тесты ловят поломку цены и личной скидки в КП, имён комнат в документе, групп света в листе монтажника</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>88e41ec</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Найдено при разбиении app.js (дыра была и раньше)</t>
-        </is>
-      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Убрать мёртвый код одиночных элементов — вместе с решением, что делать с ними в старых проектах</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>не начато</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>З10</t>
+          <t>З9</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Тесты ловят поломку перетаскивания: порог клик/перенос, отмена Esc, сохранение позиции, блокировка пробелом</t>
+          <t>Тесты ловят поломку цены и личной скидки в КП, имён комнат в документе, групп света в листе монтажника</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -996,19 +996,19 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>3bfba3e</t>
+          <t>88e41ec</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Найдено при разбиении app.js</t>
+          <t>Найдено при разбиении app.js (дыра была и раньше)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>З8</t>
+          <t>З10</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Тесты ловят поломку правки вершин контура комнаты</t>
+          <t>Тесты ловят поломку перетаскивания: порог клик/перенос, отмена Esc, сохранение позиции, блокировка пробелом</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>7cdbbf8</t>
+          <t>3bfba3e</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -1045,7 +1045,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>З11</t>
+          <t>З8</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Тесты ловят поломку инструмента «Разметка»: очистка, притяжение к точке, пересборка при удалении линии</t>
+          <t>Тесты ловят поломку правки вершин контура комнаты</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>08bcd70</t>
+          <t>7cdbbf8</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -1082,77 +1082,77 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
+          <t>З11</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>2. Надёжность кода</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Тесты ловят поломку инструмента «Разметка»: очистка, притяжение к точке, пересборка при удалении линии</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>08bcd70</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Найдено при разбиении app.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
           <t>З12</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>2. Надёжность кода</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Инструмент тестов правильно вырезает последнюю функцию модуля</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>28.09.2026</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr"/>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>Правка была в 1e647e9; тесты закрепляют её на всех модулях</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Б3</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>3. Функции по просьбе заказчика</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Поворот плана («повернуть нужно обязательно»)</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>05.10.2026</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7add36a</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Оба варианта (только чертёж / весь план) и оба угла (90° / любой); весь план — на холсте, в КП и листе монтажника; подписи прямые, цена не меняется</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Б4</t>
+          <t>Б3</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Отмена и повтор действия (undo / redo)</t>
+          <t>Поворот плана («повернуть нужно обязательно»)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1172,24 +1172,24 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>07.10.2026</t>
+          <t>05.10.2026</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>b09dc37</t>
+          <t>7add36a</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Кнопки «Отменить/Вернуть», Ctrl+Z/Y, 50 шагов: посты, стены, разметка, комнаты, окно поста, поворот, очистка, «Убрать план», чертёж; смета возвращается; настройки и вид не откатываются</t>
+          <t>Оба варианта (только чертёж / весь план) и оба угла (90° / любой); весь план — на холсте, в КП и листе монтажника; подписи прямые, цена не меняется</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Б5</t>
+          <t>Б4</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Групповое выделение («обязательно для отелей»)</t>
+          <t>Отмена и повтор действия (undo / redo)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1209,24 +1209,24 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10.10.2026</t>
+          <t>07.10.2026</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69a896b</t>
+          <t>b09dc37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Рамка мышью и Ctrl+клик, «Выделено: N», карточка группы с суммой; группу можно перетащить, сдвинуть стрелками, удалить; каждый пост в своей комнате; отмена одним шагом. Только посты</t>
+          <t>Кнопки «Отменить/Вернуть», Ctrl+Z/Y, 50 шагов: посты, стены, разметка, комнаты, окно поста, поворот, очистка, «Убрать план», чертёж; смета возвращается; настройки и вид не откатываются</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Б9</t>
+          <t>Б5</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Копирование постов («да, с избранным на N комбинаций»)</t>
+          <t>Групповое выделение («обязательно для отелей»)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1246,24 +1246,24 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11.10.2026</t>
+          <t>10.10.2026</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>aabbb78</t>
+          <t>69a896b</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Ctrl+C / Ctrl+V: копии встают под мышью в том же расположении, считаются по своей комнате, отмена одним шагом; свои номера проходных; накладка, уже подходящая комнате, не меняется (и при «Разместить»); два сообщения с крестиком. Не сделано: «избранное на N комбинаций» — вопрос заказчику. В бэклоге: В22 (автосдвиг выносит пост за стену), В23 (снятая с производства накладка).</t>
+          <t>Рамка мышью и Ctrl+клик, «Выделено: N», карточка группы с суммой; группу можно перетащить, сдвинуть стрелками, удалить; каждый пост в своей комнате; отмена одним шагом. Только посты</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>А5</t>
+          <t>Б9</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Реквизиты с галочками: какие поля показывать в КП (свои и заказчика)</t>
+          <t>Копирование постов («да, с избранным на N комбинаций»)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1283,24 +1283,24 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>03.10.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8e7129e</t>
+          <t>aabbb78</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>«Мои реквизиты» (общие для всех проектов) и «Реквизиты заказчика» (свои у проекта): ФИО, телефон и e-mail печатаются всегда, остальное — по галочке «показывать в КП»; «Разработчик» под своей галочкой. Перепроверено в браузере 11.10: снятые поля в шапке КП не печатаются, после перезагрузки всё на месте.</t>
+          <t>Ctrl+C / Ctrl+V: копии встают под мышью в том же расположении, считаются по своей комнате, отмена одним шагом; свои номера проходных; накладка, уже подходящая комнате, не меняется (и при «Разместить»); два сообщения с крестиком. Не сделано: «избранное на N комбинаций» — вопрос заказчику. В бэклоге: В22 (автосдвиг выносит пост за стену), В23 (снятая с производства накладка).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>А6</t>
+          <t>А5</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Спецификация в Excel</t>
+          <t>Реквизиты с галочками: какие поля показывать в КП (свои и заказчика)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1325,19 +1325,19 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4ace33c</t>
+          <t>8e7129e</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Кнопка «Спецификация Excel» рядом с КП: файл .xlsx с листами «Спецификация» (как в КП) и «По артикулам» (поставщику); числа — числами, итог — формулой. Перепроверено 11.10: итоги файла равны КП до копейки. Состязательной проверки не было.</t>
+          <t>«Мои реквизиты» (общие для всех проектов) и «Реквизиты заказчика» (свои у проекта): ФИО, телефон и e-mail печатаются всегда, остальное — по галочке «показывать в КП»; «Разработчик» под своей галочкой. Перепроверено в браузере 11.10: снятые поля в шапке КП не печатаются, после перезагрузки всё на месте.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Б6</t>
+          <t>А6</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1347,22 +1347,34 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Этажи</t>
+          <t>Спецификация в Excel</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>03.10.2026</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4ace33c</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Кнопка «Спецификация Excel» рядом с КП: файл .xlsx с листами «Спецификация» (как в КП) и «По артикулам» (поставщику); числа — числами, итог — формулой. Перепроверено 11.10: итоги файла равны КП до копейки. Состязательной проверки не было.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Б7</t>
+          <t>Б6</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1372,7 +1384,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Экспликация по комнатам</t>
+          <t>Этажи</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1387,7 +1399,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>А7</t>
+          <t>Б7</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1397,7 +1409,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Запоминать скидку и настройки по клиенту («у Иванова постоянно 10%»)</t>
+          <t>Экспликация по комнатам</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1412,44 +1424,32 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>В3</t>
+          <t>А7</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>4. Мелочи интерфейса</t>
+          <t>3. Функции по просьбе заказчика</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Вид «С картинками»: строка «Стандарт: не задан» / название стандарта над «Подобрать накладку»</t>
+          <t>Запоминать скидку и настройки по клиенту («у Иванова постоянно 10%»)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>660f88b</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Строка «Стандарт: …» в виде «С картинками»</t>
-        </is>
-      </c>
+          <t>не начато</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>В9</t>
+          <t>В3</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1459,22 +1459,34 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Панель «Стоимость»: процент скидки не противоречит сумме с личными скидками; поле не обрезает «%»</t>
+          <t>Вид «С картинками»: строка «Стандарт: не задан» / название стандарта над «Подобрать накладку»</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>660f88b</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Строка «Стандарт: …» в виде «С картинками»</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>В12</t>
+          <t>В9</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1484,7 +1496,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Окно поста без накладок: совет «измените отбор» один раз, нет ложного «выберите накладку» справа</t>
+          <t>Панель «Стоимость»: процент скидки не противоречит сумме с личными скидками; поле не обрезает «%»</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1499,7 +1511,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>В4</t>
+          <t>В12</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1509,7 +1521,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Подсказка «сузили: …» называет стандарт и при непустом отборе</t>
+          <t>Окно поста без накладок: совет «измените отбор» один раз, нет ложного «выберите накладку» справа</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1524,7 +1536,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>В6</t>
+          <t>В4</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1534,34 +1546,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Печать в КП — внахлёст на подпись, а не справа</t>
+          <t>Подсказка «сузили: …» называет стандарт и при непустом отборе</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>13.10.2026</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>359fad6</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Печать поверх подписи, подпись видна сквозь неё, имя под подписью не перекрыто.</t>
-        </is>
-      </c>
+          <t>не начато</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>З4</t>
+          <t>В6</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1571,37 +1571,49 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Фокус Tab не уезжает на соседнюю строку при слиянии строк скидки</t>
+          <t>Печать в КП — внахлёст на подпись, а не справа</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>359fad6</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Печать поверх подписи, подпись видна сквозь неё, имя под подписью не перекрыто.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>З3</t>
+          <t>З4</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>5. Ваше решение</t>
+          <t>4. Мелочи интерфейса</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Пост со своей скидкой, равной общей (10 и 10) — сливать ли со строкой без своей скидки</t>
+          <t>Фокус Tab не уезжает на соседнюю строку при слиянии строк скидки</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>ждёт вашего решения</t>
+          <t>не начато</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -1611,7 +1623,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>З5</t>
+          <t>З3</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1621,7 +1633,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>НДС нового проекта по умолчанию «Начислить сверху» — оставить или сменить</t>
+          <t>Пост со своей скидкой, равной общей (10 и 10) — сливать ли со строкой без своей скидки</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1636,36 +1648,32 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>А1</t>
+          <t>З5</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>6. Ждёт ответа заказчика</t>
+          <t>5. Ваше решение</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Наценка в КП — видна клиенту строкой или сразу в цене</t>
+          <t>НДС нового проекта по умолчанию «Начислить сверху» — оставить или сменить</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>ждёт заказчика</t>
+          <t>ждёт вашего решения</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Вы отложили 24.09</t>
-        </is>
-      </c>
+      <c r="G36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>А8</t>
+          <t>А1</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1675,7 +1683,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Два документа «Расчёт» и «КП» — чем «Расчёт» отличается</t>
+          <t>Наценка в КП — видна клиенту строкой или сразу в цене</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1685,12 +1693,16 @@
       </c>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Вы отложили 24.09</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Б8</t>
+          <t>А8</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1700,7 +1712,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Вертикальные / горизонтальные рамки (разные артикулы)</t>
+          <t>Два документа «Расчёт» и «КП» — чем «Расчёт» отличается</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1715,7 +1727,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Г1</t>
+          <t>Б8</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1725,7 +1737,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Подсветка клавиш, часть B (NEVE, Eikon Flat — 9,60 € за светодиод)</t>
+          <t>Вертикальные / горизонтальные рамки (разные артикулы)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1740,7 +1752,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Е1</t>
+          <t>Г1</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1750,7 +1762,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Код функции изделия — замена клавиш при смене серии; опечатка 19105.B</t>
+          <t>Подсветка клавиш, часть B (NEVE, Eikon Flat — 9,60 € за светодиод)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1765,7 +1777,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Е2</t>
+          <t>Е1</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1775,7 +1787,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Фото 698 артикулов</t>
+          <t>Код функции изделия — замена клавиш при смене серии; опечатка 19105.B</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1790,7 +1802,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Е3</t>
+          <t>Е2</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1800,7 +1812,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Подсветка NEVE / Eikon Flat; звонковые кнопки 220 В или 00935</t>
+          <t>Фото 698 артикулов</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1815,7 +1827,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Е4</t>
+          <t>Е3</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1825,7 +1837,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Аксессуары 02973, 02974, 02965.1 и таблица «механизм → аксессуар»</t>
+          <t>Подсветка NEVE / Eikon Flat; звонковые кнопки 220 В или 00935</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -1840,7 +1852,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Е5</t>
+          <t>Е4</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1850,7 +1862,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Логотип EPG в векторе, «Соглашения сторон», формат номера КП</t>
+          <t>Аксессуары 02973, 02974, 02965.1 и таблица «механизм → аксессуар»</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -1865,7 +1877,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Е6</t>
+          <t>Е5</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1875,7 +1887,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Типы пользователей; коды 2 и 4 в «Группе доступа»</t>
+          <t>Логотип EPG в векторе, «Соглашения сторон», формат номера КП</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -1890,7 +1902,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Е7</t>
+          <t>Е6</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1900,7 +1912,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Прайс со статусами (в наличии / под заказ / снят, замены), номенклатура LINEA</t>
+          <t>Типы пользователей; коды 2 и 4 в «Группе доступа»</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -1915,7 +1927,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Е8</t>
+          <t>Е7</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1925,7 +1937,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Немецкий стандарт без накладки на 3 модуля — по умолчанию 2 или 4 (сейчас 2)</t>
+          <t>Прайс со статусами (в наличии / под заказ / снят, замены), номенклатура LINEA</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -1935,45 +1947,41 @@
       </c>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Связано с З6</t>
-        </is>
-      </c>
+      <c r="G47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Д1</t>
+          <t>Е8</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>7. Сервис на продажу</t>
+          <t>6. Ждёт ответа заказчика</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Личные кабинеты, многопользовательский режим</t>
+          <t>Немецкий стандарт без накладки на 3 модуля — по умолчанию 2 или 4 (сейчас 2)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>не начато</t>
+          <t>ждёт заказчика</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Обсудить приоритеты с заказчиком</t>
+          <t>Связано с З6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Д2</t>
+          <t>Д1</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -1983,7 +1991,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Уровни доступа демо / менеджер / профи, покупка брендов, логотип и подпись по тарифу</t>
+          <t>Личные кабинеты, многопользовательский режим</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -1993,12 +2001,16 @@
       </c>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Обсудить приоритеты с заказчиком</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Д3</t>
+          <t>Д2</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2008,7 +2020,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Версии проекта и история КП; курс евро версионировать вместе с проектом</t>
+          <t>Уровни доступа демо / менеджер / профи, покупка брендов, логотип и подпись по тарифу</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2023,7 +2035,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Д4</t>
+          <t>Д3</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2033,7 +2045,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Обязательные поля проекта, проверка уникальности КП</t>
+          <t>Версии проекта и история КП; курс евро версионировать вместе с проектом</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2048,7 +2060,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Д5</t>
+          <t>Д4</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2058,7 +2070,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Сравнение спецификаций разных компаний по одному объекту</t>
+          <t>Обязательные поля проекта, проверка уникальности КП</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2073,7 +2085,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Д6</t>
+          <t>Д5</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2083,7 +2095,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Прайсы в других валютах и с другой наценкой под новые бренды</t>
+          <t>Сравнение спецификаций разных компаний по одному объекту</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2098,22 +2110,22 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Ж1</t>
+          <t>Д6</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>8. Отложено заказчиком</t>
+          <t>7. Сервис на продажу</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Распознавание плана чертежа (кнопки скрыты с 21.09)</t>
+          <t>Прайсы в других валютах и с другой наценкой под новые бренды</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>отложено заказчиком</t>
+          <t>не начато</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -2123,7 +2135,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Ж2</t>
+          <t>Ж1</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2133,7 +2145,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Межсерийные адаптеры 09623, 16723</t>
+          <t>Распознавание плана чертежа (кнопки скрыты с 21.09)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2148,7 +2160,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Ж3</t>
+          <t>Ж2</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2158,7 +2170,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Расценки работ по операциям</t>
+          <t>Межсерийные адаптеры 09623, 16723</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2173,7 +2185,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Ж4</t>
+          <t>Ж3</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -2183,7 +2195,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Битрикс</t>
+          <t>Расценки работ по операциям</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2193,49 +2205,41 @@
       </c>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Не обязателен</t>
-        </is>
-      </c>
+      <c r="G57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>В2</t>
+          <t>Ж4</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>4. Мелочи интерфейса</t>
+          <t>8. Отложено заказчиком</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Плашка «Под эту комнату накладок нет» — совет один раз</t>
+          <t>Битрикс</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>26.09.2026</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>d7204e3</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
+          <t>отложено заказчиком</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Не обязателен</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>В1</t>
+          <t>В2</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -2245,7 +2249,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Клик по табличке комнаты при «Разместить» ставит пост</t>
+          <t>Плашка «Под эту комнату накладок нет» — совет один раз</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2260,7 +2264,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>56d4916</t>
+          <t>d7204e3</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
@@ -2268,17 +2272,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Б1</t>
+          <t>В1</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>3. Функции по просьбе заказчика</t>
+          <t>4. Мелочи интерфейса</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Убрать одиночные элементы с плана (счётчик «Элементов»)</t>
+          <t>Клик по табличке комнаты при «Разместить» ставит пост</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2293,7 +2297,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>69762c3</t>
+          <t>56d4916</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -2301,7 +2305,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>А2</t>
+          <t>Б1</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -2311,7 +2315,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Скидка на отдельные позиции</t>
+          <t>Убрать одиночные элементы с плана (счётчик «Элементов»)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2326,7 +2330,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>f9c3143</t>
+          <t>69762c3</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
@@ -2334,7 +2338,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Б2</t>
+          <t>А2</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -2344,7 +2348,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Лист монтажника: «общая сборка» / «взрыв-схема»</t>
+          <t>Скидка на отдельные позиции</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2359,7 +2363,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>8511c47</t>
+          <t>f9c3143</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -2367,7 +2371,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>А4</t>
+          <t>Б2</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -2377,7 +2381,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Автонумерация КП EPG-2026-0001</t>
+          <t>Лист монтажника: «общая сборка» / «взрыв-схема»</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2387,16 +2391,20 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr"/>
+          <t>26.09.2026</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>8511c47</t>
+        </is>
+      </c>
       <c r="G63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>А3</t>
+          <t>А4</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2406,7 +2414,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>НДС — три режима</t>
+          <t>Автонумерация КП EPG-2026-0001</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -2425,17 +2433,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>В15</t>
+          <t>А3</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>1. Деньги и потеря данных</t>
+          <t>3. Функции по просьбе заказчика</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Удалил стену и нарисовал заново — комната среди других исчезает вместе с полями (у любой формы)</t>
+          <t>НДС — три режима</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -2445,34 +2453,26 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>154a9fa</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>Комната возвращается со своими полями и ценой; память в проекте</t>
-        </is>
-      </c>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>З13</t>
+          <t>В15</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>2. Надёжность кода</t>
+          <t>1. Деньги и потеря данных</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Тесты: перенос полей не должен брать точку таблички или сырой полюс (мутации MX1/MX2 не пойманы)</t>
+          <t>Удалил стену и нарисовал заново — комната среди других исчезает вместе с полями (у любой формы)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -2492,42 +2492,79 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Тесты с жёстким ожиданием; MX1/MX2 красят</t>
+          <t>Комната возвращается со своими полями и ценой; память в проекте</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>З13</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>2. Надёжность кода</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Тесты: перенос полей не должен брать точку таблички или сырой полюс (мутации MX1/MX2 не пойманы)</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>154a9fa</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Тесты с жёстким ожиданием; MX1/MX2 красят</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
           <t>З14</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>2. Надёжность кода</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Тесты: память исчезнувших комнат не должна попадать на постороннюю комнату (мутации MY1/MY2/MY8 не пойманы)</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>сделано</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>01acd84</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>Тесты Ж7–Ж9; все 8 мутаций памяти красят</t>
         </is>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2567,6 +2567,117 @@
       <c r="G68" s="2" t="inlineStr">
         <is>
           <t>Тесты Ж7–Ж9; все 8 мутаций памяти красят</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>ОЗ-2</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>1. Деньги и потеря данных</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Суппорт 21613 для всех накладок 22673 и 22683 (вкл. Tondo RN)</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>c777c9e</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Ответ заказчика 20.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>ОЗ-1</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>1. Деньги и потеря данных</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Подсветка по типу клавиши: обычные — внизу, осевые — по центру, LINEA — своя</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>0a15c54</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>+214 клавиш с подсветкой; у прежних артикул не сменился; KNX без подсветки</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>К7</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>1. Деньги и потеря данных</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Рубли в КП целыми: цена и строки вверх, скидка вниз, материалы/работы/НДС вверх</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>b7b3a65</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>КП, панель, окно поста, Excel; евро без изменений; итог = сумма строк</t>
         </is>
       </c>
     </row>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2678,6 +2678,43 @@
       <c r="G71" s="2" t="inlineStr">
         <is>
           <t>КП, панель, окно поста, Excel; евро без изменений; итог = сумма строк</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>К5</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>1. Деньги и потеря данных</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Термодатчик 02965.1 к терморегуляторам 02974/09474/30811: сам, по одному на каждый, в цене и документах; у поста «с датчиком / без», в т.ч. у поста библиотеки; строка в листе монтажника</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>22.10.2026</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>d8a298f, d61c285, 3e3d20d</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Окно поста, КП, Excel, сводная, лист монтажника; 2217 тестов; три проверки</t>
         </is>
       </c>
     </row>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2715,6 +2715,43 @@
       <c r="G72" s="2" t="inlineStr">
         <is>
           <t>Окно поста, КП, Excel, сводная, лист монтажника; 2217 тестов; три проверки</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>К8(а)</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>3. Функции по просьбе заказчика</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>До пяти вариантов отделки в комнате: вкладки в панели, выбор варианта в окне поста, размещение и «Готовые посты» по вариантам</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>24.10.2026</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>416a4f0, 118675e, 5b5d495</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Две проверки + второй проход; бэклог текстов — в ОСТАТОК К8</t>
         </is>
       </c>
     </row>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2752,6 +2752,43 @@
       <c r="G73" s="2" t="inlineStr">
         <is>
           <t>Две проверки + второй проход; бэклог текстов — в ОСТАТОК К8</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>К8г</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>3. Функции по просьбе заказчика</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Нельзя собрать несовместимое: отделка в панели комнаты и окне поста сужается сверху вниз; несовместимое сохранённое — «(не подходит)»/«нет накладок»; поиск артикула и смена варианта в окне поста</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>24.10.2026</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>d839688, f5fbd6e, 98a6e5a</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Две проверки основной части + приёмка и проход ep-adversary по починке; бэклог — в ОСТАТОК К8г</t>
         </is>
       </c>
     </row>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2789,6 +2789,43 @@
       <c r="G74" t="inlineStr">
         <is>
           <t>Две проверки основной части + приёмка и проход ep-adversary по починке; бэклог — в ОСТАТОК К8г</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>К8(б)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>3. Функции по просьбе заказчика</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>У выбора отделки написано, для какой комнаты: «Отделка накладки — X», «Подбор накладки — X»</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>24.10.2026</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>см. журнал HANDOFF 24.10</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Приёмка лично; «применить ко всем» и отделка проекта — не делаем</t>
         </is>
       </c>
     </row>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2826,6 +2826,43 @@
       <c r="G75" t="inlineStr">
         <is>
           <t>Приёмка лично; «применить ко всем» и отделка проекта — не делаем</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>К9(1)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>3. Функции по просьбе заказчика</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Прайс по шаблону: кнопка рядом со «Спецификация Excel» — скачать шаблон прайса и проверить файл заказчика (ошибки/предупреждения); конвертер каталога читает прайс по тому же правилу (js/priceSheet.js)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>25.10.2026</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1949d60, 2ca0459, 39193ac, cf99958; слияние 2f46a57</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Две проверки (проход 2 — только ep-adversary); К9-З1/К9-З2 и мелкое — в ОСТАТОК К9; К9(2)/К9(3) ждут решения о хранилище</t>
         </is>
       </c>
     </row>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2863,6 +2863,43 @@
       <c r="G76" t="inlineStr">
         <is>
           <t>Две проверки (проход 2 — только ep-adversary); К9-З1/К9-З2 и мелкое — в ОСТАТОК К9; К9(2)/К9(3) ждут решения о хранилище</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>К10</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>3. Функции по просьбе заказчика</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>План и логотип/подпись/печать из мессенджеров и айфона: JFIF, GIF, BMP, AVIF, HEIC/HEIF; формат по содержимому файла, а не по имени; под «Загрузить план» — «PNG · JPG · PDF · DXF · DWG · фото из мессенджеров»</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>25.10.2026</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>9030fab, 11cc8f5, 8cf789b</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Две проверки (ep-verify, ep-adversary) — значимых нет; логотип HEIC в открытом КП — кадр; LGPL-строка, большие фото, перетаскивание — в ОСТАТОК К10</t>
         </is>
       </c>
     </row>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -2879,7 +2879,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>План и логотип/подпись/печать из мессенджеров и айфона: JFIF, GIF, BMP, AVIF, HEIC/HEIF; формат по содержимому файла, а не по имени; под «Загрузить план» — «PNG · JPG · PDF · DXF · DWG · фото из мессенджеров»</t>
+          <t>План и логотип/подпись/печать из мессенджеров и айфона: JFIF, GIF, BMP, AVIF, HEIC/HEIF; формат по содержимому файла, а не по имени; под «Загрузить план» — «PNG · JPG · PDF · DXF · DWG · фото из мессенджеров»; большие фото и PDF-скан уменьшаются до 4000 точек и не теряются после перезагрузки; перетаскивание файла на холст</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>9030fab, 11cc8f5, 8cf789b</t>
+          <t>9030fab, 11cc8f5, 8cf789b, 6f43a91, 6016526, 7900036</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Две проверки (ep-verify, ep-adversary) — значимых нет; логотип HEIC в открытом КП — кадр; LGPL-строка, большие фото, перетаскивание — в ОСТАТОК К10</t>
+          <t>Две проверки (ep-verify, ep-adversary) по ч.1–2; остаток доделан по слову владельца, браузер и мутации — лично; бэклог: ICO, статус уменьшенного растра</t>
         </is>
       </c>
     </row>

--- a/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
+++ b/docs/ЭТАПЫ-РАЗРАБОТКИ.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2900,6 +2900,43 @@
       <c r="G77" t="inlineStr">
         <is>
           <t>Две проверки (ep-verify, ep-adversary) по ч.1–2; остаток доделан по слову владельца, браузер и мутации — лично; бэклог: ICO, статус уменьшенного растра</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>К11-3</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>3. Функции по просьбе заказчика</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Лист монтажника по галочкам: окно с наборами «Строителю»/«Клиенту» и тремя своими; лист проекта и поста печатается ровно по выбору</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>сделано</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>28.10.2026</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>b611617</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Своё окно, отдельно от КП; галочки — свойство проекта; свои наборы едут в файл проекта</t>
         </is>
       </c>
     </row>
